--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -439,7 +439,7 @@
         <v>456.15</v>
       </c>
       <c r="E2">
-        <v>462.6</v>
+        <v>457.9</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -459,19 +459,19 @@
         <v>Equity</v>
       </c>
       <c r="C3">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>1380</v>
+        <v>1163.22</v>
       </c>
       <c r="E3">
-        <v>1620</v>
+        <v>1183.8</v>
       </c>
       <c r="F3">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G3">
-        <v>2700</v>
+        <v>48</v>
       </c>
       <c r="H3" t="str">
         <v>IT Services</v>
@@ -485,19 +485,19 @@
         <v>Equity</v>
       </c>
       <c r="C4">
-        <v>300</v>
+        <v>21</v>
       </c>
       <c r="D4">
-        <v>440</v>
+        <v>307.97</v>
       </c>
       <c r="E4">
-        <v>462</v>
+        <v>286.9</v>
       </c>
       <c r="F4">
-        <v>13.75</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>3712.5</v>
+        <v>0</v>
       </c>
       <c r="H4" t="str">
         <v>FMCG / Diversified</v>
@@ -511,19 +511,19 @@
         <v>Equity</v>
       </c>
       <c r="C5">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="D5">
-        <v>420</v>
+        <v>444.41</v>
       </c>
       <c r="E5">
-        <v>480</v>
+        <v>428.6</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>2430</v>
+        <v>0</v>
       </c>
       <c r="H5" t="str">
         <v>NBFC / PSU</v>
@@ -537,19 +537,19 @@
         <v>Equity</v>
       </c>
       <c r="C6">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="D6">
-        <v>520</v>
+        <v>349.25</v>
       </c>
       <c r="E6">
-        <v>590</v>
+        <v>337.65</v>
       </c>
       <c r="F6">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>2295</v>
+        <v>0</v>
       </c>
       <c r="H6" t="str">
         <v>NBFC / PSU</v>
@@ -563,19 +563,19 @@
         <v>Equity</v>
       </c>
       <c r="C7">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="D7">
-        <v>200</v>
+        <v>185.6</v>
       </c>
       <c r="E7">
-        <v>205</v>
+        <v>183.22</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>1620</v>
+        <v>0</v>
       </c>
       <c r="H7" t="str">
         <v>Lubricants</v>
@@ -589,19 +589,19 @@
         <v>Equity</v>
       </c>
       <c r="C8">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D8">
-        <v>430</v>
+        <v>734.84</v>
       </c>
       <c r="E8">
-        <v>460</v>
+        <v>352.6</v>
       </c>
       <c r="F8">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="H8" t="str">
         <v>Mining / Metals</v>
@@ -615,19 +615,19 @@
         <v>REIT</v>
       </c>
       <c r="C9">
-        <v>200</v>
+        <v>13</v>
       </c>
       <c r="D9">
-        <v>135</v>
+        <v>156.39</v>
       </c>
       <c r="E9">
-        <v>140</v>
+        <v>155.2</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>1620</v>
+        <v>0</v>
       </c>
       <c r="H9" t="str">
         <v>Retail REIT</v>
@@ -641,19 +641,19 @@
         <v>REIT</v>
       </c>
       <c r="C10">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="D10">
-        <v>340</v>
+        <v>465.39</v>
       </c>
       <c r="E10">
-        <v>345</v>
+        <v>462.49</v>
       </c>
       <c r="F10">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>2835</v>
+        <v>0</v>
       </c>
       <c r="H10" t="str">
         <v>Office REIT</v>
@@ -667,19 +667,19 @@
         <v>REIT</v>
       </c>
       <c r="C11">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="D11">
-        <v>285</v>
+        <v>325.69</v>
       </c>
       <c r="E11">
-        <v>290</v>
+        <v>318.88</v>
       </c>
       <c r="F11">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="H11" t="str">
         <v>Office REIT</v>
@@ -693,19 +693,19 @@
         <v>REIT</v>
       </c>
       <c r="C12">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D12">
-        <v>360</v>
+        <v>423.08</v>
       </c>
       <c r="E12">
-        <v>370</v>
+        <v>427.17</v>
       </c>
       <c r="F12">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>2070</v>
+        <v>0</v>
       </c>
       <c r="H12" t="str">
         <v>Office REIT</v>
@@ -719,19 +719,19 @@
         <v>InvIT</v>
       </c>
       <c r="C13">
-        <v>200</v>
+        <v>16</v>
       </c>
       <c r="D13">
-        <v>100</v>
+        <v>123.33</v>
       </c>
       <c r="E13">
-        <v>105</v>
+        <v>124.47</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="H13" t="str">
         <v>Infrastructure</v>
@@ -745,19 +745,19 @@
         <v>InvIT</v>
       </c>
       <c r="C14">
-        <v>300</v>
+        <v>105</v>
       </c>
       <c r="D14">
-        <v>75</v>
+        <v>60.36</v>
       </c>
       <c r="E14">
-        <v>80</v>
+        <v>60.46</v>
       </c>
       <c r="F14">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>2025</v>
+        <v>0</v>
       </c>
       <c r="H14" t="str">
         <v>Infrastructure</v>
@@ -771,19 +771,19 @@
         <v>InvIT</v>
       </c>
       <c r="C15">
-        <v>200</v>
+        <v>31</v>
       </c>
       <c r="D15">
-        <v>160</v>
+        <v>169.74</v>
       </c>
       <c r="E15">
-        <v>165</v>
+        <v>171.43</v>
       </c>
       <c r="F15">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="H15" t="str">
         <v>Power Grid</v>
@@ -797,19 +797,19 @@
         <v>InvIT</v>
       </c>
       <c r="C16">
-        <v>150</v>
+        <v>106</v>
       </c>
       <c r="D16">
-        <v>108</v>
+        <v>92.6</v>
       </c>
       <c r="E16">
-        <v>112</v>
+        <v>92.81</v>
       </c>
       <c r="F16">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>1417.5</v>
+        <v>0</v>
       </c>
       <c r="H16" t="str">
         <v>Power Grid</v>
